--- a/public/inputs/y12-portuguese-a-level - input.xlsx
+++ b/public/inputs/y12-portuguese-a-level - input.xlsx
@@ -441,10 +441,9 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unidade 0 · Conheceo teuA Level Português</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Unidade 0 · Conhece o teu A Level Português</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -457,7 +456,6 @@
           <t>Unidade 1 · Português de nível avançado</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -467,10 +465,9 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unidade 2 · Pensamento críticoe</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Unidade 2 · Pensamento crítico e</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -480,10 +477,9 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unidade 3 · Vocabulário, registoe precisão</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>Unidade 3 · Vocabulário, registo e precisão</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -496,7 +492,6 @@
           <t>Unidade 4 · Gramática avançada ao serviço da</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -509,7 +504,6 @@
           <t>Unidade 5 · Construir uma apresentação de</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -522,7 +516,6 @@
           <t>Unidade 6 · Defender uma opinião</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -535,7 +528,6 @@
           <t>Unidade 7 · Conversar espontaneamente</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -545,10 +537,9 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unidade 8 · Sociedadee cultura lusófona</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>Unidade 8 · Sociedade e cultura lusófona</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -561,7 +552,6 @@
           <t>Unidade 9 · Speaking Practice</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -574,7 +564,6 @@
           <t>Unidade 10 · Leitura avançada</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -584,10 +573,9 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unidade 11 · Vocabulárioe manipulação</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>Unidade 11 · Vocabulário e manipulação</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -597,10 +585,9 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unidade 12 · Compreensãoe inferência</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>Unidade 12 · Compreensão e inferência</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -613,7 +600,6 @@
           <t>Unidade 13 · Comparar dois textos</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -623,10 +609,9 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unidade 14 · Síntesee resposta pessoal (~140</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>Unidade 14 · Síntese e resposta pessoal (~140</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -639,7 +624,6 @@
           <t>Unidade 15 · Reading &amp; Writing Practice</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -649,10 +633,9 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unidade 16 · Como construir um ensaioA</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>Unidade 16 · Como construir um ensaio A</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -665,7 +648,6 @@
           <t>Unidade 17 · Law and order</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -678,7 +660,6 @@
           <t>Unidade 18 · Health and ﬁtness</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -691,7 +672,6 @@
           <t>Unidade 19 · Travel and tourism</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -704,7 +684,6 @@
           <t>Unidade 20 · Scientiﬁc and medical advances</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -717,7 +696,6 @@
           <t>Unidade 21 · Pollution</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -730,7 +708,6 @@
           <t>Unidade 22 · Essay Practice</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -740,10 +717,9 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Unidade 23 · Como estudar literatura paraA</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>Unidade 23 · Como estudar literatura para A</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -756,7 +732,6 @@
           <t>Unidade 24 · Section 1 · O Meu Pé de Laranja</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -769,7 +744,6 @@
           <t>Unidade 25 · Section 1 · A Rainha Ginga</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -782,7 +756,6 @@
           <t>Unidade 26 · Section 1 · O Retorno</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -795,7 +768,6 @@
           <t>Unidade 27 · Section 2 · Veromar</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -808,7 +780,6 @@
           <t>Unidade 28 · Section 2 · Equador</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -821,7 +792,6 @@
           <t>Unidade 29 · Section 2 · Luanda, Lisboa,</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -831,10 +801,9 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Unidade 30 · Como respondera uma pergunta</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>Unidade 30 · Como responder a uma pergunta</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -847,7 +816,6 @@
           <t>Unidade 31 · Como escrever um ensaio</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -860,7 +828,6 @@
           <t>Unidade 32 · Texts Exam Practice</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -873,7 +840,6 @@
           <t>Unidade 33 · Pensar como um examinador</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -886,7 +852,6 @@
           <t>Unidade 34 · Gestão do tempo</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -899,7 +864,6 @@
           <t>Unidade 35 · Erros que fazem perder pontos</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -912,7 +876,6 @@
           <t>Unidade 36 · Prática cronometrada</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -925,7 +888,6 @@
           <t>Unidade 37 · Simulação 1</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -938,7 +900,6 @@
           <t>Unidade 38 · Simulação 2</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -951,7 +912,6 @@
           <t>Unidade 39 · Simulação ﬁnal</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
